--- a/2023_zscore/zscore_2023_vacancy_rate.xlsx
+++ b/2023_zscore/zscore_2023_vacancy_rate.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D285"/>
+  <dimension ref="A1:E285"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -372,6 +372,11 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>zscore_raw</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>zscore</t>
         </is>
       </c>
@@ -391,6 +396,9 @@
       <c r="D2">
         <v>1.290559033589375</v>
       </c>
+      <c r="E2">
+        <v>1.290559033589375</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -407,6 +415,9 @@
       <c r="D3">
         <v>-0.09806563661688311</v>
       </c>
+      <c r="E3">
+        <v>-0.09806563661688311</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -423,6 +434,9 @@
       <c r="D4">
         <v>0.9688877642870455</v>
       </c>
+      <c r="E4">
+        <v>0.9688877642870455</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -439,6 +453,9 @@
       <c r="D5">
         <v>1.090692404324832</v>
       </c>
+      <c r="E5">
+        <v>1.090692404324832</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -455,6 +472,9 @@
       <c r="D6">
         <v>1.000591243497598</v>
       </c>
+      <c r="E6">
+        <v>1.000591243497598</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -471,6 +491,9 @@
       <c r="D7">
         <v>0.4445728602550135</v>
       </c>
+      <c r="E7">
+        <v>0.4445728602550135</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -487,6 +510,9 @@
       <c r="D8">
         <v>0.3832681329551937</v>
       </c>
+      <c r="E8">
+        <v>0.3832681329551937</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -503,6 +529,9 @@
       <c r="D9">
         <v>0.93813133810419</v>
       </c>
+      <c r="E9">
+        <v>0.93813133810419</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -519,6 +548,9 @@
       <c r="D10">
         <v>1.290559033589375</v>
       </c>
+      <c r="E10">
+        <v>1.290559033589375</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -535,6 +567,9 @@
       <c r="D11">
         <v>0.50007024271939</v>
       </c>
+      <c r="E11">
+        <v>0.50007024271939</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -551,6 +586,9 @@
       <c r="D12">
         <v>0.5455556982246941</v>
       </c>
+      <c r="E12">
+        <v>0.5455556982246941</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -567,6 +605,9 @@
       <c r="D13">
         <v>0.88454301728384</v>
       </c>
+      <c r="E13">
+        <v>0.88454301728384</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -583,6 +624,9 @@
       <c r="D14">
         <v>0.4378031919774043</v>
       </c>
+      <c r="E14">
+        <v>0.4378031919774043</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -599,6 +643,9 @@
       <c r="D15">
         <v>0.612132985238995</v>
       </c>
+      <c r="E15">
+        <v>0.612132985238995</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -615,6 +662,9 @@
       <c r="D16">
         <v>1.045526219516094</v>
       </c>
+      <c r="E16">
+        <v>1.045526219516094</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -631,6 +681,9 @@
       <c r="D17">
         <v>-0.285414392371054</v>
       </c>
+      <c r="E17">
+        <v>-0.285414392371054</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -647,6 +700,9 @@
       <c r="D18">
         <v>1.290559033589375</v>
       </c>
+      <c r="E18">
+        <v>1.290559033589375</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -663,6 +719,9 @@
       <c r="D19">
         <v>0.8833576708512119</v>
       </c>
+      <c r="E19">
+        <v>0.8833576708512119</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -679,6 +738,9 @@
       <c r="D20">
         <v>1.081738373641905</v>
       </c>
+      <c r="E20">
+        <v>1.081738373641905</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -695,6 +757,9 @@
       <c r="D21">
         <v>0.7587261696338273</v>
       </c>
+      <c r="E21">
+        <v>0.7587261696338273</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -711,6 +776,9 @@
       <c r="D22">
         <v>0.6837594336725387</v>
       </c>
+      <c r="E22">
+        <v>0.6837594336725387</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -727,6 +795,9 @@
       <c r="D23">
         <v>0.8647089015447764</v>
       </c>
+      <c r="E23">
+        <v>0.8647089015447764</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -743,6 +814,9 @@
       <c r="D24">
         <v>-0.35118981866777</v>
       </c>
+      <c r="E24">
+        <v>-0.35118981866777</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -759,6 +833,9 @@
       <c r="D25">
         <v>1.066671183167088</v>
       </c>
+      <c r="E25">
+        <v>1.066671183167088</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -775,6 +852,9 @@
       <c r="D26">
         <v>-0.3755277834362942</v>
       </c>
+      <c r="E26">
+        <v>-0.3755277834362942</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -791,6 +871,9 @@
       <c r="D27">
         <v>0.3726353699465898</v>
       </c>
+      <c r="E27">
+        <v>0.3726353699465898</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -807,6 +890,9 @@
       <c r="D28">
         <v>-0.5267225527803385</v>
       </c>
+      <c r="E28">
+        <v>-0.5267225527803385</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -823,6 +909,9 @@
       <c r="D29">
         <v>-1.267151134487314</v>
       </c>
+      <c r="E29">
+        <v>-1.267151134487314</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -839,6 +928,9 @@
       <c r="D30">
         <v>-2.324460928300811</v>
       </c>
+      <c r="E30">
+        <v>-2.324460928300811</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -855,6 +947,9 @@
       <c r="D31">
         <v>0.9523905243090935</v>
       </c>
+      <c r="E31">
+        <v>0.9523905243090935</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -871,6 +966,9 @@
       <c r="D32">
         <v>0.378199286664274</v>
       </c>
+      <c r="E32">
+        <v>0.378199286664274</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -887,6 +985,9 @@
       <c r="D33">
         <v>1.290559033589375</v>
       </c>
+      <c r="E33">
+        <v>1.290559033589375</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -903,6 +1004,9 @@
       <c r="D34">
         <v>1.290559033589375</v>
       </c>
+      <c r="E34">
+        <v>1.290559033589375</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -919,6 +1023,9 @@
       <c r="D35">
         <v>0.9767177672795057</v>
       </c>
+      <c r="E35">
+        <v>0.9767177672795057</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -935,6 +1042,9 @@
       <c r="D36">
         <v>0.1238500921329971</v>
       </c>
+      <c r="E36">
+        <v>0.1238500921329971</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -951,6 +1061,9 @@
       <c r="D37">
         <v>0.3016373624416043</v>
       </c>
+      <c r="E37">
+        <v>0.3016373624416043</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -967,6 +1080,9 @@
       <c r="D38">
         <v>0.1412497219957873</v>
       </c>
+      <c r="E38">
+        <v>0.1412497219957873</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -983,6 +1099,9 @@
       <c r="D39">
         <v>0.2166760919116915</v>
       </c>
+      <c r="E39">
+        <v>0.2166760919116915</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -999,6 +1118,9 @@
       <c r="D40">
         <v>0.3204369731578463</v>
       </c>
+      <c r="E40">
+        <v>0.3204369731578463</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -1015,6 +1137,9 @@
       <c r="D41">
         <v>0.8918874628478084</v>
       </c>
+      <c r="E41">
+        <v>0.8918874628478084</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -1031,6 +1156,9 @@
       <c r="D42">
         <v>-0.2852128199999855</v>
       </c>
+      <c r="E42">
+        <v>-0.2852128199999855</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -1047,6 +1175,9 @@
       <c r="D43">
         <v>-0.7720244230401984</v>
       </c>
+      <c r="E43">
+        <v>-0.7720244230401984</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -1063,6 +1194,9 @@
       <c r="D44">
         <v>0.3611300689280235</v>
       </c>
+      <c r="E44">
+        <v>0.3611300689280235</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -1079,6 +1213,9 @@
       <c r="D45">
         <v>0.2073604808513549</v>
       </c>
+      <c r="E45">
+        <v>0.2073604808513549</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -1095,6 +1232,9 @@
       <c r="D46">
         <v>0.009963225307465068</v>
       </c>
+      <c r="E46">
+        <v>0.009963225307465068</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -1111,6 +1251,9 @@
       <c r="D47">
         <v>0.1688984506613934</v>
       </c>
+      <c r="E47">
+        <v>0.1688984506613934</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -1127,6 +1270,9 @@
       <c r="D48">
         <v>1.025165326656137</v>
       </c>
+      <c r="E48">
+        <v>1.025165326656137</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -1143,6 +1289,9 @@
       <c r="D49">
         <v>1.290559033589375</v>
       </c>
+      <c r="E49">
+        <v>1.290559033589375</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -1159,6 +1308,9 @@
       <c r="D50">
         <v>0.1242550923613653</v>
       </c>
+      <c r="E50">
+        <v>0.1242550923613653</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -1175,6 +1327,9 @@
       <c r="D51">
         <v>-0.01786153940267233</v>
       </c>
+      <c r="E51">
+        <v>-0.01786153940267233</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -1191,6 +1346,9 @@
       <c r="D52">
         <v>0.58793481974069</v>
       </c>
+      <c r="E52">
+        <v>0.58793481974069</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -1207,6 +1365,9 @@
       <c r="D53">
         <v>0.7075698677690748</v>
       </c>
+      <c r="E53">
+        <v>0.7075698677690748</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -1223,6 +1384,9 @@
       <c r="D54">
         <v>-0.9524476629684211</v>
       </c>
+      <c r="E54">
+        <v>-0.9524476629684211</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -1239,6 +1403,9 @@
       <c r="D55">
         <v>-0.4639120823803459</v>
       </c>
+      <c r="E55">
+        <v>-0.4639120823803459</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -1255,6 +1422,9 @@
       <c r="D56">
         <v>1.135660296847953</v>
       </c>
+      <c r="E56">
+        <v>1.135660296847953</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -1271,6 +1441,9 @@
       <c r="D57">
         <v>-0.001471009579939027</v>
       </c>
+      <c r="E57">
+        <v>-0.001471009579939027</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58">
@@ -1287,6 +1460,9 @@
       <c r="D58">
         <v>0.05008041234339004</v>
       </c>
+      <c r="E58">
+        <v>0.05008041234339004</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -1303,6 +1479,9 @@
       <c r="D59">
         <v>-1.153643286791603</v>
       </c>
+      <c r="E59">
+        <v>-1.153643286791603</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60">
@@ -1319,6 +1498,9 @@
       <c r="D60">
         <v>-0.740847126516433</v>
       </c>
+      <c r="E60">
+        <v>-0.740847126516433</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -1335,6 +1517,9 @@
       <c r="D61">
         <v>-2.366245149515125</v>
       </c>
+      <c r="E61">
+        <v>-2.366245149515125</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62">
@@ -1351,6 +1536,9 @@
       <c r="D62">
         <v>0.3890199939074727</v>
       </c>
+      <c r="E62">
+        <v>0.3890199939074727</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63">
@@ -1367,6 +1555,9 @@
       <c r="D63">
         <v>-0.8274850442113922</v>
       </c>
+      <c r="E63">
+        <v>-0.8274850442113922</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64">
@@ -1383,6 +1574,9 @@
       <c r="D64">
         <v>0.3111225978589757</v>
       </c>
+      <c r="E64">
+        <v>0.3111225978589757</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65">
@@ -1399,6 +1593,9 @@
       <c r="D65">
         <v>-0.2716117480066319</v>
       </c>
+      <c r="E65">
+        <v>-0.2716117480066319</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66">
@@ -1415,6 +1612,9 @@
       <c r="D66">
         <v>-0.9002171577812468</v>
       </c>
+      <c r="E66">
+        <v>-0.9002171577812468</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67">
@@ -1431,6 +1631,9 @@
       <c r="D67">
         <v>0.7999855654136456</v>
       </c>
+      <c r="E67">
+        <v>0.7999855654136456</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68">
@@ -1447,6 +1650,9 @@
       <c r="D68">
         <v>1.134727439528891</v>
       </c>
+      <c r="E68">
+        <v>1.134727439528891</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69">
@@ -1463,6 +1669,9 @@
       <c r="D69">
         <v>1.014119093858234</v>
       </c>
+      <c r="E69">
+        <v>1.014119093858234</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70">
@@ -1479,6 +1688,9 @@
       <c r="D70">
         <v>0.3993923129623791</v>
       </c>
+      <c r="E70">
+        <v>0.3993923129623791</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71">
@@ -1495,6 +1707,9 @@
       <c r="D71">
         <v>1.088319588946959</v>
       </c>
+      <c r="E71">
+        <v>1.088319588946959</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72">
@@ -1511,6 +1726,9 @@
       <c r="D72">
         <v>1.037030556254429</v>
       </c>
+      <c r="E72">
+        <v>1.037030556254429</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73">
@@ -1527,6 +1745,9 @@
       <c r="D73">
         <v>1.065399599132645</v>
       </c>
+      <c r="E73">
+        <v>1.065399599132645</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74">
@@ -1543,6 +1764,9 @@
       <c r="D74">
         <v>0.864374901441212</v>
       </c>
+      <c r="E74">
+        <v>0.864374901441212</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75">
@@ -1559,6 +1783,9 @@
       <c r="D75">
         <v>0.6852876309916948</v>
       </c>
+      <c r="E75">
+        <v>0.6852876309916948</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76">
@@ -1575,6 +1802,9 @@
       <c r="D76">
         <v>0.7941661269308113</v>
       </c>
+      <c r="E76">
+        <v>0.7941661269308113</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77">
@@ -1591,6 +1821,9 @@
       <c r="D77">
         <v>-0.1038488953081632</v>
       </c>
+      <c r="E77">
+        <v>-0.1038488953081632</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78">
@@ -1607,6 +1840,9 @@
       <c r="D78">
         <v>1.188157260543825</v>
       </c>
+      <c r="E78">
+        <v>1.188157260543825</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79">
@@ -1623,6 +1859,9 @@
       <c r="D79">
         <v>0.2601201552918254</v>
       </c>
+      <c r="E79">
+        <v>0.2601201552918254</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80">
@@ -1639,6 +1878,9 @@
       <c r="D80">
         <v>0.7006596025572287</v>
       </c>
+      <c r="E80">
+        <v>0.7006596025572287</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81">
@@ -1655,6 +1897,9 @@
       <c r="D81">
         <v>0.831634699539083</v>
       </c>
+      <c r="E81">
+        <v>0.831634699539083</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82">
@@ -1671,6 +1916,9 @@
       <c r="D82">
         <v>0.4274605503525156</v>
       </c>
+      <c r="E82">
+        <v>0.4274605503525156</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83">
@@ -1687,6 +1935,9 @@
       <c r="D83">
         <v>0.9740593109940868</v>
       </c>
+      <c r="E83">
+        <v>0.9740593109940868</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84">
@@ -1703,6 +1954,9 @@
       <c r="D84">
         <v>-0.2817830644066599</v>
       </c>
+      <c r="E84">
+        <v>-0.2817830644066599</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85">
@@ -1719,6 +1973,9 @@
       <c r="D85">
         <v>0.8367032835766598</v>
       </c>
+      <c r="E85">
+        <v>0.8367032835766598</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86">
@@ -1735,6 +1992,9 @@
       <c r="D86">
         <v>-2.104593827222384</v>
       </c>
+      <c r="E86">
+        <v>-2.104593827222384</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87">
@@ -1751,6 +2011,9 @@
       <c r="D87">
         <v>-0.3252126283513412</v>
       </c>
+      <c r="E87">
+        <v>-0.3252126283513412</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88">
@@ -1767,6 +2030,9 @@
       <c r="D88">
         <v>-0.9964138977612476</v>
       </c>
+      <c r="E88">
+        <v>-0.9964138977612476</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89">
@@ -1783,6 +2049,9 @@
       <c r="D89">
         <v>-0.1159293191912578</v>
       </c>
+      <c r="E89">
+        <v>-0.1159293191912578</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90">
@@ -1799,6 +2068,9 @@
       <c r="D90">
         <v>0.432026949199997</v>
       </c>
+      <c r="E90">
+        <v>0.432026949199997</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91">
@@ -1815,6 +2087,9 @@
       <c r="D91">
         <v>-0.2893540362562572</v>
       </c>
+      <c r="E91">
+        <v>-0.2893540362562572</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92">
@@ -1831,6 +2106,9 @@
       <c r="D92">
         <v>0.8402121296962942</v>
       </c>
+      <c r="E92">
+        <v>0.8402121296962942</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93">
@@ -1847,6 +2125,9 @@
       <c r="D93">
         <v>-0.06441865927980263</v>
       </c>
+      <c r="E93">
+        <v>-0.06441865927980263</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94">
@@ -1863,6 +2144,9 @@
       <c r="D94">
         <v>0.03072857583595839</v>
       </c>
+      <c r="E94">
+        <v>0.03072857583595839</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95">
@@ -1879,6 +2163,9 @@
       <c r="D95">
         <v>-0.7759896459994706</v>
       </c>
+      <c r="E95">
+        <v>-0.7759896459994706</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96">
@@ -1895,6 +2182,9 @@
       <c r="D96">
         <v>-0.0369753872091474</v>
       </c>
+      <c r="E96">
+        <v>-0.0369753872091474</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97">
@@ -1911,6 +2201,9 @@
       <c r="D97">
         <v>1.126569759043089</v>
       </c>
+      <c r="E97">
+        <v>1.126569759043089</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98">
@@ -1927,6 +2220,9 @@
       <c r="D98">
         <v>-0.1358888441089574</v>
       </c>
+      <c r="E98">
+        <v>-0.1358888441089574</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99">
@@ -1943,6 +2239,9 @@
       <c r="D99">
         <v>0.2250706603614013</v>
       </c>
+      <c r="E99">
+        <v>0.2250706603614013</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100">
@@ -1959,6 +2258,9 @@
       <c r="D100">
         <v>1.076871705994203</v>
       </c>
+      <c r="E100">
+        <v>1.076871705994203</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101">
@@ -1975,6 +2277,9 @@
       <c r="D101">
         <v>0.7173516695536717</v>
       </c>
+      <c r="E101">
+        <v>0.7173516695536717</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102">
@@ -1991,6 +2296,9 @@
       <c r="D102">
         <v>0.9829827495390498</v>
       </c>
+      <c r="E102">
+        <v>0.9829827495390498</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103">
@@ -2007,6 +2315,9 @@
       <c r="D103">
         <v>0.5503020058100947</v>
       </c>
+      <c r="E103">
+        <v>0.5503020058100947</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104">
@@ -2023,6 +2334,9 @@
       <c r="D104">
         <v>1.290559033589375</v>
       </c>
+      <c r="E104">
+        <v>1.290559033589375</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105">
@@ -2039,6 +2353,9 @@
       <c r="D105">
         <v>-0.3506582923708585</v>
       </c>
+      <c r="E105">
+        <v>-0.3506582923708585</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106">
@@ -2055,6 +2372,9 @@
       <c r="D106">
         <v>0.6433864666301876</v>
       </c>
+      <c r="E106">
+        <v>0.6433864666301876</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107">
@@ -2071,6 +2391,9 @@
       <c r="D107">
         <v>0.03302248178143478</v>
       </c>
+      <c r="E107">
+        <v>0.03302248178143478</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108">
@@ -2087,6 +2410,9 @@
       <c r="D108">
         <v>0.2660361822802846</v>
       </c>
+      <c r="E108">
+        <v>0.2660361822802846</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109">
@@ -2103,6 +2429,9 @@
       <c r="D109">
         <v>-0.639267051567301</v>
       </c>
+      <c r="E109">
+        <v>-0.639267051567301</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110">
@@ -2119,6 +2448,9 @@
       <c r="D110">
         <v>0.2529051154055917</v>
       </c>
+      <c r="E110">
+        <v>0.2529051154055917</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111">
@@ -2135,6 +2467,9 @@
       <c r="D111">
         <v>0.4693956107810811</v>
       </c>
+      <c r="E111">
+        <v>0.4693956107810811</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112">
@@ -2151,6 +2486,9 @@
       <c r="D112">
         <v>0.8004934054428131</v>
       </c>
+      <c r="E112">
+        <v>0.8004934054428131</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113">
@@ -2167,6 +2505,9 @@
       <c r="D113">
         <v>0.8369204655950609</v>
       </c>
+      <c r="E113">
+        <v>0.8369204655950609</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114">
@@ -2183,6 +2524,9 @@
       <c r="D114">
         <v>0.6635112057681115</v>
       </c>
+      <c r="E114">
+        <v>0.6635112057681115</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115">
@@ -2199,6 +2543,9 @@
       <c r="D115">
         <v>0.2852981831514176</v>
       </c>
+      <c r="E115">
+        <v>0.2852981831514176</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116">
@@ -2215,6 +2562,9 @@
       <c r="D116">
         <v>0.2951209415556532</v>
       </c>
+      <c r="E116">
+        <v>0.2951209415556532</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117">
@@ -2231,6 +2581,9 @@
       <c r="D117">
         <v>-0.5457245724416798</v>
       </c>
+      <c r="E117">
+        <v>-0.5457245724416798</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118">
@@ -2247,6 +2600,9 @@
       <c r="D118">
         <v>-1.911203070301497</v>
       </c>
+      <c r="E118">
+        <v>-1.911203070301497</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119">
@@ -2263,6 +2619,9 @@
       <c r="D119">
         <v>-0.4412589598801968</v>
       </c>
+      <c r="E119">
+        <v>-0.4412589598801968</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120">
@@ -2279,6 +2638,9 @@
       <c r="D120">
         <v>-0.6101706555443898</v>
       </c>
+      <c r="E120">
+        <v>-0.6101706555443898</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121">
@@ -2295,6 +2657,9 @@
       <c r="D121">
         <v>-1.423184640487106</v>
       </c>
+      <c r="E121">
+        <v>-1.423184640487106</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122">
@@ -2311,6 +2676,9 @@
       <c r="D122">
         <v>0.5557970208625389</v>
       </c>
+      <c r="E122">
+        <v>0.5557970208625389</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123">
@@ -2327,6 +2695,9 @@
       <c r="D123">
         <v>0.9707328014004947</v>
       </c>
+      <c r="E123">
+        <v>0.9707328014004947</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124">
@@ -2343,6 +2714,9 @@
       <c r="D124">
         <v>-1.354003163906603</v>
       </c>
+      <c r="E124">
+        <v>-1.354003163906603</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125">
@@ -2359,6 +2733,9 @@
       <c r="D125">
         <v>0.5402314602956549</v>
       </c>
+      <c r="E125">
+        <v>0.5402314602956549</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126">
@@ -2375,6 +2752,9 @@
       <c r="D126">
         <v>0.4292154241187331</v>
       </c>
+      <c r="E126">
+        <v>0.4292154241187331</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127">
@@ -2391,6 +2771,9 @@
       <c r="D127">
         <v>0.7012046209116009</v>
       </c>
+      <c r="E127">
+        <v>0.7012046209116009</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128">
@@ -2407,6 +2790,9 @@
       <c r="D128">
         <v>-0.4238634980066448</v>
       </c>
+      <c r="E128">
+        <v>-0.4238634980066448</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129">
@@ -2423,6 +2809,9 @@
       <c r="D129">
         <v>0.1295682825825948</v>
       </c>
+      <c r="E129">
+        <v>0.1295682825825948</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130">
@@ -2439,6 +2828,9 @@
       <c r="D130">
         <v>-0.4852081836946378</v>
       </c>
+      <c r="E130">
+        <v>-0.4852081836946378</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131">
@@ -2455,6 +2847,9 @@
       <c r="D131">
         <v>0.6369941120832214</v>
       </c>
+      <c r="E131">
+        <v>0.6369941120832214</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132">
@@ -2471,6 +2866,9 @@
       <c r="D132">
         <v>-1.864462017689952</v>
       </c>
+      <c r="E132">
+        <v>-1.864462017689952</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133">
@@ -2487,6 +2885,9 @@
       <c r="D133">
         <v>-1.191941354487407</v>
       </c>
+      <c r="E133">
+        <v>-1.191941354487407</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134">
@@ -2503,6 +2904,9 @@
       <c r="D134">
         <v>-1.496336213117989</v>
       </c>
+      <c r="E134">
+        <v>-1.496336213117989</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135">
@@ -2519,6 +2923,9 @@
       <c r="D135">
         <v>-0.4481291563754988</v>
       </c>
+      <c r="E135">
+        <v>-0.4481291563754988</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136">
@@ -2535,6 +2942,9 @@
       <c r="D136">
         <v>-1.54507011169572</v>
       </c>
+      <c r="E136">
+        <v>-1.54507011169572</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137">
@@ -2551,6 +2961,9 @@
       <c r="D137">
         <v>-0.1505448309316405</v>
       </c>
+      <c r="E137">
+        <v>-0.1505448309316405</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138">
@@ -2567,6 +2980,9 @@
       <c r="D138">
         <v>-0.5023484562538649</v>
       </c>
+      <c r="E138">
+        <v>-0.5023484562538649</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139">
@@ -2583,6 +2999,9 @@
       <c r="D139">
         <v>-1.879863805500682</v>
       </c>
+      <c r="E139">
+        <v>-1.879863805500682</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140">
@@ -2599,6 +3018,9 @@
       <c r="D140">
         <v>-0.5793320546878119</v>
       </c>
+      <c r="E140">
+        <v>-0.5793320546878119</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141">
@@ -2615,6 +3037,9 @@
       <c r="D141">
         <v>-3.278812883249169</v>
       </c>
+      <c r="E141">
+        <v>-3.278812883249169</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142">
@@ -2631,6 +3056,9 @@
       <c r="D142">
         <v>-0.8704134214310374</v>
       </c>
+      <c r="E142">
+        <v>-0.8704134214310374</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143">
@@ -2647,6 +3075,9 @@
       <c r="D143">
         <v>-0.8630874218981782</v>
       </c>
+      <c r="E143">
+        <v>-0.8630874218981782</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144">
@@ -2663,6 +3094,9 @@
       <c r="D144">
         <v>0.5564562100271662</v>
       </c>
+      <c r="E144">
+        <v>0.5564562100271662</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145">
@@ -2679,6 +3113,9 @@
       <c r="D145">
         <v>-1.603051590179175</v>
       </c>
+      <c r="E145">
+        <v>-1.603051590179175</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146">
@@ -2695,6 +3132,9 @@
       <c r="D146">
         <v>-0.03080310452431795</v>
       </c>
+      <c r="E146">
+        <v>-0.03080310452431795</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147">
@@ -2711,6 +3151,9 @@
       <c r="D147">
         <v>-2.616301963345254</v>
       </c>
+      <c r="E147">
+        <v>-2.616301963345254</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148">
@@ -2727,6 +3170,9 @@
       <c r="D148">
         <v>-0.9939613798723995</v>
       </c>
+      <c r="E148">
+        <v>-0.9939613798723995</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149">
@@ -2743,6 +3189,9 @@
       <c r="D149">
         <v>-0.1433864208230309</v>
       </c>
+      <c r="E149">
+        <v>-0.1433864208230309</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150">
@@ -2759,6 +3208,9 @@
       <c r="D150">
         <v>0.5920338581817879</v>
       </c>
+      <c r="E150">
+        <v>0.5920338581817879</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151">
@@ -2775,6 +3227,9 @@
       <c r="D151">
         <v>-1.586910308635978</v>
       </c>
+      <c r="E151">
+        <v>-1.586910308635978</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152">
@@ -2791,6 +3246,9 @@
       <c r="D152">
         <v>-1.555451725424733</v>
       </c>
+      <c r="E152">
+        <v>-1.555451725424733</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153">
@@ -2807,6 +3265,9 @@
       <c r="D153">
         <v>-0.9817772710006033</v>
       </c>
+      <c r="E153">
+        <v>-0.9817772710006033</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154">
@@ -2823,6 +3284,9 @@
       <c r="D154">
         <v>-1.237301878163637</v>
       </c>
+      <c r="E154">
+        <v>-1.237301878163637</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155">
@@ -2839,6 +3303,9 @@
       <c r="D155">
         <v>0.4908757834217402</v>
       </c>
+      <c r="E155">
+        <v>0.4908757834217402</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156">
@@ -2855,6 +3322,9 @@
       <c r="D156">
         <v>-1.821955346151228</v>
       </c>
+      <c r="E156">
+        <v>-1.821955346151228</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157">
@@ -2871,6 +3341,9 @@
       <c r="D157">
         <v>0.05399966646117128</v>
       </c>
+      <c r="E157">
+        <v>0.05399966646117128</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158">
@@ -2887,6 +3360,9 @@
       <c r="D158">
         <v>0.1231575462635137</v>
       </c>
+      <c r="E158">
+        <v>0.1231575462635137</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159">
@@ -2903,6 +3379,9 @@
       <c r="D159">
         <v>0.2412115594235872</v>
       </c>
+      <c r="E159">
+        <v>0.2412115594235872</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160">
@@ -2919,6 +3398,9 @@
       <c r="D160">
         <v>-1.136786719064837</v>
       </c>
+      <c r="E160">
+        <v>-1.136786719064837</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161">
@@ -2935,6 +3417,9 @@
       <c r="D161">
         <v>-1.621058639687085</v>
       </c>
+      <c r="E161">
+        <v>-1.621058639687085</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162">
@@ -2951,6 +3436,9 @@
       <c r="D162">
         <v>-1.803610251868152</v>
       </c>
+      <c r="E162">
+        <v>-1.803610251868152</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163">
@@ -2967,6 +3455,9 @@
       <c r="D163">
         <v>-2.36542759508262</v>
       </c>
+      <c r="E163">
+        <v>-2.36542759508262</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164">
@@ -2983,6 +3474,9 @@
       <c r="D164">
         <v>-0.2461444889150484</v>
       </c>
+      <c r="E164">
+        <v>-0.2461444889150484</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165">
@@ -2999,6 +3493,9 @@
       <c r="D165">
         <v>-2.479673531815016</v>
       </c>
+      <c r="E165">
+        <v>-2.479673531815016</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166">
@@ -3015,6 +3512,9 @@
       <c r="D166">
         <v>-0.7518430135859623</v>
       </c>
+      <c r="E166">
+        <v>-0.7518430135859623</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167">
@@ -3031,6 +3531,9 @@
       <c r="D167">
         <v>-0.05615495707602632</v>
       </c>
+      <c r="E167">
+        <v>-0.05615495707602632</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168">
@@ -3047,6 +3550,9 @@
       <c r="D168">
         <v>-1.759005221980439</v>
       </c>
+      <c r="E168">
+        <v>-1.759005221980439</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169">
@@ -3063,6 +3569,9 @@
       <c r="D169">
         <v>0.2006626213875873</v>
       </c>
+      <c r="E169">
+        <v>0.2006626213875873</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170">
@@ -3079,6 +3588,9 @@
       <c r="D170">
         <v>-0.539445587899576</v>
       </c>
+      <c r="E170">
+        <v>-0.539445587899576</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171">
@@ -3095,6 +3607,9 @@
       <c r="D171">
         <v>-1.529214867061973</v>
       </c>
+      <c r="E171">
+        <v>-1.529214867061973</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172">
@@ -3111,6 +3626,9 @@
       <c r="D172">
         <v>-0.9733895271526086</v>
       </c>
+      <c r="E172">
+        <v>-0.9733895271526086</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173">
@@ -3127,6 +3645,9 @@
       <c r="D173">
         <v>-0.5776597185827053</v>
       </c>
+      <c r="E173">
+        <v>-0.5776597185827053</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174">
@@ -3143,6 +3664,9 @@
       <c r="D174">
         <v>-0.5506405545746879</v>
       </c>
+      <c r="E174">
+        <v>-0.5506405545746879</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175">
@@ -3159,6 +3683,9 @@
       <c r="D175">
         <v>-2.253086748545624</v>
       </c>
+      <c r="E175">
+        <v>-2.253086748545624</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176">
@@ -3175,6 +3702,9 @@
       <c r="D176">
         <v>-0.8094261550041216</v>
       </c>
+      <c r="E176">
+        <v>-0.8094261550041216</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177">
@@ -3191,6 +3721,9 @@
       <c r="D177">
         <v>-1.688441432102764</v>
       </c>
+      <c r="E177">
+        <v>-1.688441432102764</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178">
@@ -3207,6 +3740,9 @@
       <c r="D178">
         <v>-1.582738501637716</v>
       </c>
+      <c r="E178">
+        <v>-1.582738501637716</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179">
@@ -3223,6 +3759,9 @@
       <c r="D179">
         <v>-1.283672492372943</v>
       </c>
+      <c r="E179">
+        <v>-1.283672492372943</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180">
@@ -3239,6 +3778,9 @@
       <c r="D180">
         <v>-0.4680105159780951</v>
       </c>
+      <c r="E180">
+        <v>-0.4680105159780951</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181">
@@ -3255,6 +3797,9 @@
       <c r="D181">
         <v>0.1027564022004803</v>
       </c>
+      <c r="E181">
+        <v>0.1027564022004803</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182">
@@ -3271,6 +3816,9 @@
       <c r="D182">
         <v>-2.792476196307776</v>
       </c>
+      <c r="E182">
+        <v>-2.792476196307776</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183">
@@ -3287,6 +3835,9 @@
       <c r="D183">
         <v>-1.039034756936418</v>
       </c>
+      <c r="E183">
+        <v>-1.039034756936418</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184">
@@ -3303,6 +3854,9 @@
       <c r="D184">
         <v>-1.663903604997554</v>
       </c>
+      <c r="E184">
+        <v>-1.663903604997554</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185">
@@ -3319,6 +3873,9 @@
       <c r="D185">
         <v>-1.619336851779636</v>
       </c>
+      <c r="E185">
+        <v>-1.619336851779636</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186">
@@ -3335,6 +3892,9 @@
       <c r="D186">
         <v>-1.204521080903442</v>
       </c>
+      <c r="E186">
+        <v>-1.204521080903442</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187">
@@ -3351,6 +3911,9 @@
       <c r="D187">
         <v>-0.4676967658354425</v>
       </c>
+      <c r="E187">
+        <v>-0.4676967658354425</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188">
@@ -3367,6 +3930,9 @@
       <c r="D188">
         <v>-1.565485002677502</v>
       </c>
+      <c r="E188">
+        <v>-1.565485002677502</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189">
@@ -3383,6 +3949,9 @@
       <c r="D189">
         <v>-0.9029534877147166</v>
       </c>
+      <c r="E189">
+        <v>-0.9029534877147166</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190">
@@ -3399,6 +3968,9 @@
       <c r="D190">
         <v>-2.368597656571621</v>
       </c>
+      <c r="E190">
+        <v>-2.368597656571621</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191">
@@ -3415,6 +3987,9 @@
       <c r="D191">
         <v>0.3652247409045699</v>
       </c>
+      <c r="E191">
+        <v>0.3652247409045699</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192">
@@ -3431,6 +4006,9 @@
       <c r="D192">
         <v>0.8692961561089911</v>
       </c>
+      <c r="E192">
+        <v>0.8692961561089911</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193">
@@ -3447,6 +4025,9 @@
       <c r="D193">
         <v>1.290559033589375</v>
       </c>
+      <c r="E193">
+        <v>1.290559033589375</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194">
@@ -3463,6 +4044,9 @@
       <c r="D194">
         <v>-0.6366773171000391</v>
       </c>
+      <c r="E194">
+        <v>-0.6366773171000391</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195">
@@ -3479,6 +4063,9 @@
       <c r="D195">
         <v>0.2816551105860869</v>
       </c>
+      <c r="E195">
+        <v>0.2816551105860869</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196">
@@ -3495,6 +4082,9 @@
       <c r="D196">
         <v>0.4336879959974679</v>
       </c>
+      <c r="E196">
+        <v>0.4336879959974679</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197">
@@ -3511,6 +4101,9 @@
       <c r="D197">
         <v>-1.703946971646222</v>
       </c>
+      <c r="E197">
+        <v>-1.703946971646222</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198">
@@ -3527,6 +4120,9 @@
       <c r="D198">
         <v>0.8405528647533661</v>
       </c>
+      <c r="E198">
+        <v>0.8405528647533661</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199">
@@ -3543,6 +4139,9 @@
       <c r="D199">
         <v>-0.7271993676534381</v>
       </c>
+      <c r="E199">
+        <v>-0.7271993676534381</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200">
@@ -3559,6 +4158,9 @@
       <c r="D200">
         <v>0.4129645856469165</v>
       </c>
+      <c r="E200">
+        <v>0.4129645856469165</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201">
@@ -3575,6 +4177,9 @@
       <c r="D201">
         <v>0.827949851058842</v>
       </c>
+      <c r="E201">
+        <v>0.827949851058842</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202">
@@ -3591,6 +4196,9 @@
       <c r="D202">
         <v>-0.3547073482737209</v>
       </c>
+      <c r="E202">
+        <v>-0.3547073482737209</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203">
@@ -3607,6 +4215,9 @@
       <c r="D203">
         <v>0.417926044115497</v>
       </c>
+      <c r="E203">
+        <v>0.417926044115497</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204">
@@ -3623,6 +4234,9 @@
       <c r="D204">
         <v>0.6100581240978511</v>
       </c>
+      <c r="E204">
+        <v>0.6100581240978511</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205">
@@ -3639,6 +4253,9 @@
       <c r="D205">
         <v>0.3715150276884738</v>
       </c>
+      <c r="E205">
+        <v>0.3715150276884738</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206">
@@ -3655,6 +4272,9 @@
       <c r="D206">
         <v>-1.349126424080889</v>
       </c>
+      <c r="E206">
+        <v>-1.349126424080889</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207">
@@ -3671,6 +4291,9 @@
       <c r="D207">
         <v>0.6571155617314361</v>
       </c>
+      <c r="E207">
+        <v>0.6571155617314361</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208">
@@ -3687,6 +4310,9 @@
       <c r="D208">
         <v>0.8538325720426552</v>
       </c>
+      <c r="E208">
+        <v>0.8538325720426552</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209">
@@ -3703,6 +4329,9 @@
       <c r="D209">
         <v>-0.4187100104889751</v>
       </c>
+      <c r="E209">
+        <v>-0.4187100104889751</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210">
@@ -3719,6 +4348,9 @@
       <c r="D210">
         <v>0.1197476965264981</v>
       </c>
+      <c r="E210">
+        <v>0.1197476965264981</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211">
@@ -3735,6 +4367,9 @@
       <c r="D211">
         <v>-0.2353093062077603</v>
       </c>
+      <c r="E211">
+        <v>-0.2353093062077603</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212">
@@ -3751,6 +4386,9 @@
       <c r="D212">
         <v>-0.1993402600955366</v>
       </c>
+      <c r="E212">
+        <v>-0.1993402600955366</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213">
@@ -3767,6 +4405,9 @@
       <c r="D213">
         <v>0.2325296396954134</v>
       </c>
+      <c r="E213">
+        <v>0.2325296396954134</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214">
@@ -3783,6 +4424,9 @@
       <c r="D214">
         <v>0.3426929677208074</v>
       </c>
+      <c r="E214">
+        <v>0.3426929677208074</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215">
@@ -3799,6 +4443,9 @@
       <c r="D215">
         <v>1.12470885017922</v>
       </c>
+      <c r="E215">
+        <v>1.12470885017922</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216">
@@ -3815,6 +4462,9 @@
       <c r="D216">
         <v>0.5833363167049141</v>
       </c>
+      <c r="E216">
+        <v>0.5833363167049141</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217">
@@ -3831,6 +4481,9 @@
       <c r="D217">
         <v>1.290559033589375</v>
       </c>
+      <c r="E217">
+        <v>1.290559033589375</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218">
@@ -3847,6 +4500,9 @@
       <c r="D218">
         <v>-0.2046164467464765</v>
       </c>
+      <c r="E218">
+        <v>-0.2046164467464765</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219">
@@ -3863,6 +4519,9 @@
       <c r="D219">
         <v>0.1045010560978303</v>
       </c>
+      <c r="E219">
+        <v>0.1045010560978303</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220">
@@ -3879,6 +4538,9 @@
       <c r="D220">
         <v>0.8734975534256219</v>
       </c>
+      <c r="E220">
+        <v>0.8734975534256219</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221">
@@ -3895,6 +4557,9 @@
       <c r="D221">
         <v>0.8352722564725692</v>
       </c>
+      <c r="E221">
+        <v>0.8352722564725692</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222">
@@ -3911,6 +4576,9 @@
       <c r="D222">
         <v>1.080135790741585</v>
       </c>
+      <c r="E222">
+        <v>1.080135790741585</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223">
@@ -3927,6 +4595,9 @@
       <c r="D223">
         <v>-0.143340167004814</v>
       </c>
+      <c r="E223">
+        <v>-0.143340167004814</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224">
@@ -3943,6 +4614,9 @@
       <c r="D224">
         <v>1.093122521530329</v>
       </c>
+      <c r="E224">
+        <v>1.093122521530329</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225">
@@ -3959,6 +4633,9 @@
       <c r="D225">
         <v>0.7600457352887448</v>
       </c>
+      <c r="E225">
+        <v>0.7600457352887448</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226">
@@ -3975,6 +4652,9 @@
       <c r="D226">
         <v>0.5455527428004822</v>
       </c>
+      <c r="E226">
+        <v>0.5455527428004822</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227">
@@ -3991,6 +4671,9 @@
       <c r="D227">
         <v>1.015288127566625</v>
       </c>
+      <c r="E227">
+        <v>1.015288127566625</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228">
@@ -4007,6 +4690,9 @@
       <c r="D228">
         <v>0.7072483383387815</v>
       </c>
+      <c r="E228">
+        <v>0.7072483383387815</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229">
@@ -4023,6 +4709,9 @@
       <c r="D229">
         <v>1.290559033589375</v>
       </c>
+      <c r="E229">
+        <v>1.290559033589375</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230">
@@ -4039,6 +4728,9 @@
       <c r="D230">
         <v>0.9613535640765117</v>
       </c>
+      <c r="E230">
+        <v>0.9613535640765117</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231">
@@ -4055,6 +4747,9 @@
       <c r="D231">
         <v>0.5373962888432329</v>
       </c>
+      <c r="E231">
+        <v>0.5373962888432329</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232">
@@ -4071,6 +4766,9 @@
       <c r="D232">
         <v>0.1127222606070841</v>
       </c>
+      <c r="E232">
+        <v>0.1127222606070841</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233">
@@ -4087,6 +4785,9 @@
       <c r="D233">
         <v>-2.405722362674969</v>
       </c>
+      <c r="E233">
+        <v>-2.405722362674969</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234">
@@ -4103,6 +4804,9 @@
       <c r="D234">
         <v>0.5699270595688243</v>
       </c>
+      <c r="E234">
+        <v>0.5699270595688243</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235">
@@ -4119,6 +4823,9 @@
       <c r="D235">
         <v>-1.806125935617819</v>
       </c>
+      <c r="E235">
+        <v>-1.806125935617819</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236">
@@ -4135,6 +4842,9 @@
       <c r="D236">
         <v>-0.1697573273394018</v>
       </c>
+      <c r="E236">
+        <v>-0.1697573273394018</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237">
@@ -4151,6 +4861,9 @@
       <c r="D237">
         <v>0.7475466164722047</v>
       </c>
+      <c r="E237">
+        <v>0.7475466164722047</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238">
@@ -4167,6 +4880,9 @@
       <c r="D238">
         <v>0.2408384580994394</v>
       </c>
+      <c r="E238">
+        <v>0.2408384580994394</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239">
@@ -4183,6 +4899,9 @@
       <c r="D239">
         <v>-0.7371670589754903</v>
       </c>
+      <c r="E239">
+        <v>-0.7371670589754903</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240">
@@ -4199,6 +4918,9 @@
       <c r="D240">
         <v>-0.9542544585530331</v>
       </c>
+      <c r="E240">
+        <v>-0.9542544585530331</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241">
@@ -4215,6 +4937,9 @@
       <c r="D241">
         <v>-0.02355778719410099</v>
       </c>
+      <c r="E241">
+        <v>-0.02355778719410099</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242">
@@ -4231,6 +4956,9 @@
       <c r="D242">
         <v>1.290559033589375</v>
       </c>
+      <c r="E242">
+        <v>1.290559033589375</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243">
@@ -4247,6 +4975,9 @@
       <c r="D243">
         <v>0.6842693818491421</v>
       </c>
+      <c r="E243">
+        <v>0.6842693818491421</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244">
@@ -4263,6 +4994,9 @@
       <c r="D244">
         <v>1.051295993677581</v>
       </c>
+      <c r="E244">
+        <v>1.051295993677581</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245">
@@ -4279,6 +5013,9 @@
       <c r="D245">
         <v>1.290559033589375</v>
       </c>
+      <c r="E245">
+        <v>1.290559033589375</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246">
@@ -4295,6 +5032,9 @@
       <c r="D246">
         <v>-1.124734454100302</v>
       </c>
+      <c r="E246">
+        <v>-1.124734454100302</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247">
@@ -4311,6 +5051,9 @@
       <c r="D247">
         <v>0.5673811066487727</v>
       </c>
+      <c r="E247">
+        <v>0.5673811066487727</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248">
@@ -4327,6 +5070,9 @@
       <c r="D248">
         <v>0.447203813655446</v>
       </c>
+      <c r="E248">
+        <v>0.447203813655446</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249">
@@ -4343,6 +5089,9 @@
       <c r="D249">
         <v>0.03987071175700316</v>
       </c>
+      <c r="E249">
+        <v>0.03987071175700316</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250">
@@ -4359,6 +5108,9 @@
       <c r="D250">
         <v>0.4120360490675798</v>
       </c>
+      <c r="E250">
+        <v>0.4120360490675798</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251">
@@ -4375,6 +5127,9 @@
       <c r="D251">
         <v>1.133405432368251</v>
       </c>
+      <c r="E251">
+        <v>1.133405432368251</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252">
@@ -4391,6 +5146,9 @@
       <c r="D252">
         <v>-0.2696219922135085</v>
       </c>
+      <c r="E252">
+        <v>-0.2696219922135085</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253">
@@ -4407,6 +5165,9 @@
       <c r="D253">
         <v>-0.2758317073264109</v>
       </c>
+      <c r="E253">
+        <v>-0.2758317073264109</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254">
@@ -4423,6 +5184,9 @@
       <c r="D254">
         <v>-0.6423102074403295</v>
       </c>
+      <c r="E254">
+        <v>-0.6423102074403295</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255">
@@ -4439,6 +5203,9 @@
       <c r="D255">
         <v>0.9404755979212306</v>
       </c>
+      <c r="E255">
+        <v>0.9404755979212306</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256">
@@ -4455,6 +5222,9 @@
       <c r="D256">
         <v>0.6924651014628739</v>
       </c>
+      <c r="E256">
+        <v>0.6924651014628739</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257">
@@ -4471,6 +5241,9 @@
       <c r="D257">
         <v>1.242318198318698</v>
       </c>
+      <c r="E257">
+        <v>1.242318198318698</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258">
@@ -4487,6 +5260,9 @@
       <c r="D258">
         <v>1.146950269052574</v>
       </c>
+      <c r="E258">
+        <v>1.146950269052574</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259">
@@ -4503,6 +5279,9 @@
       <c r="D259">
         <v>1.122875660494383</v>
       </c>
+      <c r="E259">
+        <v>1.122875660494383</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260">
@@ -4519,6 +5298,9 @@
       <c r="D260">
         <v>1.290559033589375</v>
       </c>
+      <c r="E260">
+        <v>1.290559033589375</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261">
@@ -4535,6 +5317,9 @@
       <c r="D261">
         <v>0.972720124890665</v>
       </c>
+      <c r="E261">
+        <v>0.972720124890665</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262">
@@ -4551,6 +5336,9 @@
       <c r="D262">
         <v>0.5297786711096997</v>
       </c>
+      <c r="E262">
+        <v>0.5297786711096997</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263">
@@ -4567,6 +5355,9 @@
       <c r="D263">
         <v>0.8647089015447764</v>
       </c>
+      <c r="E263">
+        <v>0.8647089015447764</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264">
@@ -4583,6 +5374,9 @@
       <c r="D264">
         <v>0.7968347745948237</v>
       </c>
+      <c r="E264">
+        <v>0.7968347745948237</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265">
@@ -4599,6 +5393,9 @@
       <c r="D265">
         <v>1.260932543149716</v>
       </c>
+      <c r="E265">
+        <v>1.260932543149716</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266">
@@ -4615,6 +5412,9 @@
       <c r="D266">
         <v>1.290559033589375</v>
       </c>
+      <c r="E266">
+        <v>1.290559033589375</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267">
@@ -4631,6 +5431,9 @@
       <c r="D267">
         <v>0.9201908509016195</v>
       </c>
+      <c r="E267">
+        <v>0.9201908509016195</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268">
@@ -4647,6 +5450,9 @@
       <c r="D268">
         <v>0.8448056792696703</v>
       </c>
+      <c r="E268">
+        <v>0.8448056792696703</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269">
@@ -4663,6 +5469,9 @@
       <c r="D269">
         <v>1.140094647665463</v>
       </c>
+      <c r="E269">
+        <v>1.140094647665463</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270">
@@ -4679,6 +5488,9 @@
       <c r="D270">
         <v>1.157121390917378</v>
       </c>
+      <c r="E270">
+        <v>1.157121390917378</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271">
@@ -4695,6 +5507,9 @@
       <c r="D271">
         <v>1.290559033589375</v>
       </c>
+      <c r="E271">
+        <v>1.290559033589375</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272">
@@ -4711,6 +5526,9 @@
       <c r="D272">
         <v>1.290559033589375</v>
       </c>
+      <c r="E272">
+        <v>1.290559033589375</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273">
@@ -4727,6 +5545,9 @@
       <c r="D273">
         <v>-0.2595153716195147</v>
       </c>
+      <c r="E273">
+        <v>-0.2595153716195147</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274">
@@ -4743,6 +5564,9 @@
       <c r="D274">
         <v>-1.443650999948658</v>
       </c>
+      <c r="E274">
+        <v>-1.443650999948658</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275">
@@ -4759,6 +5583,9 @@
       <c r="D275">
         <v>0.1475748577973995</v>
       </c>
+      <c r="E275">
+        <v>0.1475748577973995</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276">
@@ -4775,6 +5602,9 @@
       <c r="D276">
         <v>-0.6795315955139412</v>
       </c>
+      <c r="E276">
+        <v>-0.6795315955139412</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277">
@@ -4791,6 +5621,9 @@
       <c r="D277">
         <v>1.162235069999489</v>
       </c>
+      <c r="E277">
+        <v>1.162235069999489</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278">
@@ -4807,6 +5640,9 @@
       <c r="D278">
         <v>-0.8366540661932135</v>
       </c>
+      <c r="E278">
+        <v>-0.8366540661932135</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279">
@@ -4823,6 +5659,9 @@
       <c r="D279">
         <v>-1.841067292221783</v>
       </c>
+      <c r="E279">
+        <v>-1.841067292221783</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280">
@@ -4849,6 +5688,9 @@
       <c r="D281">
         <v>-0.3361230715095141</v>
       </c>
+      <c r="E281">
+        <v>-0.3361230715095141</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282">
@@ -4865,6 +5707,9 @@
       <c r="D282">
         <v>-0.7494256031365538</v>
       </c>
+      <c r="E282">
+        <v>-0.7494256031365538</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283">
@@ -4881,6 +5726,9 @@
       <c r="D283">
         <v>1.284506793093083</v>
       </c>
+      <c r="E283">
+        <v>1.284506793093083</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284">
@@ -4897,6 +5745,9 @@
       <c r="D284">
         <v>-2.160691026448837</v>
       </c>
+      <c r="E284">
+        <v>-2.160691026448837</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285">
@@ -4911,6 +5762,9 @@
         <v>12.18026796589525</v>
       </c>
       <c r="D285">
+        <v>-0.2136618956790002</v>
+      </c>
+      <c r="E285">
         <v>-0.2136618956790002</v>
       </c>
     </row>
